--- a/shared_github_workshop.xlsx
+++ b/shared_github_workshop.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PRKD\Git testing\Testing\test\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PRKD\Git testing\Test\test\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:20001_{ECA13E2A-10CA-4120-A187-6760B7D102E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0581745-BB31-412B-A0BB-F57FB2E198F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,6 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Tasks!$A$1:$O$25</definedName>
   </definedNames>
   <calcPr calcId="191029" forceFullCalc="1"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -400,9 +399,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="3">
-    <numFmt numFmtId="165" formatCode="dd/mm/yyyy"/>
-    <numFmt numFmtId="166" formatCode="0.0;[Red]\(0.0\);\-"/>
-    <numFmt numFmtId="167" formatCode="[=1]&quot;Yes&quot;;[=0]&quot;No&quot;"/>
+    <numFmt numFmtId="164" formatCode="dd/mm/yyyy"/>
+    <numFmt numFmtId="165" formatCode="0.0;[Red]\(0.0\);\-"/>
+    <numFmt numFmtId="166" formatCode="[=1]&quot;Yes&quot;;[=0]&quot;No&quot;"/>
   </numFmts>
   <fonts count="16" x14ac:knownFonts="1">
     <font>
@@ -550,34 +549,34 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
     <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="166" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="9" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="167" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="165" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="1" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="10" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="11" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="11" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="11" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="11" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -1313,7 +1312,7 @@
         <v>16</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>17</v>
+        <v>117</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>18</v>
